--- a/data/availability/projects/hyde-park-developments/hyde-park-central.xlsx
+++ b/data/availability/projects/hyde-park-developments/hyde-park-central.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1309,7 +1309,6 @@
       <c r="G2" t="n">
         <v>130</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1320,7 +1319,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1366,7 +1365,6 @@
       <c r="G3" t="n">
         <v>135</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1377,7 +1375,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1423,7 +1421,6 @@
       <c r="G4" t="n">
         <v>117</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1434,7 +1431,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1480,7 +1477,6 @@
       <c r="G5" t="n">
         <v>135</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1491,7 +1487,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1537,7 +1533,6 @@
       <c r="G6" t="n">
         <v>117</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1548,7 +1543,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1594,7 +1589,6 @@
       <c r="G7" t="n">
         <v>135</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1605,7 +1599,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1651,7 +1645,6 @@
       <c r="G8" t="n">
         <v>135</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1662,7 +1655,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1708,7 +1701,6 @@
       <c r="G9" t="n">
         <v>135</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1719,7 +1711,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1765,7 +1757,6 @@
       <c r="G10" t="n">
         <v>71</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1776,7 +1767,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1822,7 +1813,6 @@
       <c r="G11" t="n">
         <v>135</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1833,7 +1823,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1879,7 +1869,6 @@
       <c r="G12" t="n">
         <v>136</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1890,7 +1879,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1936,7 +1925,6 @@
       <c r="G13" t="n">
         <v>136</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1947,7 +1935,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1993,7 +1981,6 @@
       <c r="G14" t="n">
         <v>136</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2004,7 +1991,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2050,7 +2037,6 @@
       <c r="G15" t="n">
         <v>102</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2061,7 +2047,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2107,7 +2093,6 @@
       <c r="G16" t="n">
         <v>70</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2118,7 +2103,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2164,7 +2149,6 @@
       <c r="G17" t="n">
         <v>117</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2175,7 +2159,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2221,7 +2205,6 @@
       <c r="G18" t="n">
         <v>148</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2232,7 +2215,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2278,7 +2261,6 @@
       <c r="G19" t="n">
         <v>148</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2289,7 +2271,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2335,7 +2317,6 @@
       <c r="G20" t="n">
         <v>69</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2346,7 +2327,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2392,7 +2373,6 @@
       <c r="G21" t="n">
         <v>70</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2403,7 +2383,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2449,7 +2429,6 @@
       <c r="G22" t="n">
         <v>156</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2460,7 +2439,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2506,7 +2485,6 @@
       <c r="G23" t="n">
         <v>156</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2517,7 +2495,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2563,7 +2541,6 @@
       <c r="G24" t="n">
         <v>156</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2574,7 +2551,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2620,7 +2597,6 @@
       <c r="G25" t="n">
         <v>71</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2631,7 +2607,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2677,7 +2653,6 @@
       <c r="G26" t="n">
         <v>65</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2688,7 +2663,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2734,7 +2709,6 @@
       <c r="G27" t="n">
         <v>183</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2745,7 +2719,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2791,7 +2765,6 @@
       <c r="G28" t="n">
         <v>117</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2802,7 +2775,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2848,7 +2821,6 @@
       <c r="G29" t="n">
         <v>102</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2859,7 +2831,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2905,7 +2877,6 @@
       <c r="G30" t="n">
         <v>185</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2916,7 +2887,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2962,7 +2933,6 @@
       <c r="G31" t="n">
         <v>106</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2973,7 +2943,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3019,7 +2989,6 @@
       <c r="G32" t="n">
         <v>100</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3030,7 +2999,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3076,7 +3045,6 @@
       <c r="G33" t="n">
         <v>70</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3087,7 +3055,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3133,7 +3101,6 @@
       <c r="G34" t="n">
         <v>71</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3144,7 +3111,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3190,7 +3157,6 @@
       <c r="G35" t="n">
         <v>185</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3201,7 +3167,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3247,7 +3213,6 @@
       <c r="G36" t="n">
         <v>70</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3258,7 +3223,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3304,7 +3269,6 @@
       <c r="G37" t="n">
         <v>104</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3315,7 +3279,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3361,7 +3325,6 @@
       <c r="G38" t="n">
         <v>63</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3372,7 +3335,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3418,7 +3381,6 @@
       <c r="G39" t="n">
         <v>70</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3429,7 +3391,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3475,7 +3437,6 @@
       <c r="G40" t="n">
         <v>106</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3486,7 +3447,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3532,7 +3493,6 @@
       <c r="G41" t="n">
         <v>106</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3543,7 +3503,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3589,7 +3549,6 @@
       <c r="G42" t="n">
         <v>70</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3600,7 +3559,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3646,7 +3605,6 @@
       <c r="G43" t="n">
         <v>104</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3657,7 +3615,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3703,7 +3661,6 @@
       <c r="G44" t="n">
         <v>106</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3714,7 +3671,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3760,7 +3717,6 @@
       <c r="G45" t="n">
         <v>104</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3771,7 +3727,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3817,7 +3773,6 @@
       <c r="G46" t="n">
         <v>70</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3828,7 +3783,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3874,7 +3829,6 @@
       <c r="G47" t="n">
         <v>106</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3885,7 +3839,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3931,7 +3885,6 @@
       <c r="G48" t="n">
         <v>106</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3942,7 +3895,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3988,7 +3941,6 @@
       <c r="G49" t="n">
         <v>112</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3999,7 +3951,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4045,7 +3997,6 @@
       <c r="G50" t="n">
         <v>66</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4056,7 +4007,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4102,7 +4053,6 @@
       <c r="G51" t="n">
         <v>133</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4113,7 +4063,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4159,7 +4109,6 @@
       <c r="G52" t="n">
         <v>178</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4170,7 +4119,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4216,7 +4165,6 @@
       <c r="G53" t="n">
         <v>133</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4227,7 +4175,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4273,7 +4221,6 @@
       <c r="G54" t="n">
         <v>65</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4284,7 +4231,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4330,7 +4277,6 @@
       <c r="G55" t="n">
         <v>178</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4341,7 +4287,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4387,7 +4333,6 @@
       <c r="G56" t="n">
         <v>71</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4398,7 +4343,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4444,7 +4389,6 @@
       <c r="G57" t="n">
         <v>178</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4455,7 +4399,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4501,7 +4445,6 @@
       <c r="G58" t="n">
         <v>199</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4512,7 +4455,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4558,7 +4501,6 @@
       <c r="G59" t="n">
         <v>116</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4569,7 +4511,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4615,7 +4557,6 @@
       <c r="G60" t="n">
         <v>199</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4626,7 +4567,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4672,7 +4613,6 @@
       <c r="G61" t="n">
         <v>178</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4683,7 +4623,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4729,7 +4669,6 @@
       <c r="G62" t="n">
         <v>116</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4740,7 +4679,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4786,7 +4725,6 @@
       <c r="G63" t="n">
         <v>116</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4797,7 +4735,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4843,7 +4781,6 @@
       <c r="G64" t="n">
         <v>199</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4854,7 +4791,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4900,7 +4837,6 @@
       <c r="G65" t="n">
         <v>178</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4911,7 +4847,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4957,7 +4893,6 @@
       <c r="G66" t="n">
         <v>178</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4968,7 +4903,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5014,7 +4949,6 @@
       <c r="G67" t="n">
         <v>116</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5025,7 +4959,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5071,7 +5005,6 @@
       <c r="G68" t="n">
         <v>192</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5082,7 +5015,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5128,7 +5061,6 @@
       <c r="G69" t="n">
         <v>211</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5139,7 +5071,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5185,7 +5117,6 @@
       <c r="G70" t="n">
         <v>155</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5196,7 +5127,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5242,7 +5173,6 @@
       <c r="G71" t="n">
         <v>155</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5253,7 +5183,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5314,7 +5244,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5375,7 +5305,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5436,7 +5366,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5497,7 +5427,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5558,7 +5488,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5619,7 +5549,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5680,7 +5610,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5741,7 +5671,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5802,7 +5732,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5863,7 +5793,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5924,7 +5854,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5985,7 +5915,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6046,7 +5976,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6107,7 +6037,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6168,7 +6098,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6229,7 +6159,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6290,7 +6220,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6351,7 +6281,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6412,7 +6342,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6473,7 +6403,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6534,7 +6464,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6595,7 +6525,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6656,7 +6586,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6702,7 +6632,6 @@
       <c r="G95" t="n">
         <v>114.282313</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6713,7 +6642,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6759,7 +6688,6 @@
       <c r="G96" t="n">
         <v>114.282313</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6770,7 +6698,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6816,7 +6744,6 @@
       <c r="G97" t="n">
         <v>111.8010899</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6827,7 +6754,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6873,7 +6800,6 @@
       <c r="G98" t="n">
         <v>93.35967302</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6884,7 +6810,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6930,7 +6856,6 @@
       <c r="G99" t="n">
         <v>150.1264601</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6941,7 +6866,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6987,7 +6912,6 @@
       <c r="G100" t="n">
         <v>150.1264601</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6998,7 +6922,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7044,7 +6968,6 @@
       <c r="G101" t="n">
         <v>150.1264601</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7055,7 +6978,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7101,7 +7024,6 @@
       <c r="G102" t="n">
         <v>101.4277929</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7112,7 +7034,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7158,7 +7080,6 @@
       <c r="G103" t="n">
         <v>93.35967302</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7169,7 +7090,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7215,7 +7136,6 @@
       <c r="G104" t="n">
         <v>93.35967302</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7226,7 +7146,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7272,7 +7192,6 @@
       <c r="G105" t="n">
         <v>114.106267</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7283,7 +7202,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7329,7 +7248,6 @@
       <c r="G106" t="n">
         <v>114.106267</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7340,7 +7258,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7386,7 +7304,6 @@
       <c r="G107" t="n">
         <v>93.35967302</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7397,7 +7314,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7443,7 +7360,6 @@
       <c r="G108" t="n">
         <v>93.35967302</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7454,7 +7370,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7500,7 +7416,6 @@
       <c r="G109" t="n">
         <v>93.35967302</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7511,7 +7426,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7557,7 +7472,6 @@
       <c r="G110" t="n">
         <v>114.282313</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7568,7 +7482,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7614,7 +7528,6 @@
       <c r="G111" t="n">
         <v>150.1264601</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7625,7 +7538,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7671,7 +7584,6 @@
       <c r="G112" t="n">
         <v>114</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7682,7 +7594,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7728,7 +7640,6 @@
       <c r="G113" t="n">
         <v>101.4277929</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7739,7 +7650,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7785,7 +7696,6 @@
       <c r="G114" t="n">
         <v>111.8010899</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7796,7 +7706,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7842,7 +7752,6 @@
       <c r="G115" t="n">
         <v>93.35967302</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7853,7 +7762,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7899,7 +7808,6 @@
       <c r="G116" t="n">
         <v>70.05901470000001</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7910,7 +7818,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7956,7 +7864,6 @@
       <c r="G117" t="n">
         <v>131.1569926</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7967,7 +7874,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8013,7 +7920,6 @@
       <c r="G118" t="n">
         <v>111.8010899</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8024,7 +7930,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2029-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
